--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486359_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486359_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>E. WEMBI</t>
+          <t>F. ZURBRIGGEN</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.4549</v>
+        <v>1.6087</v>
       </c>
       <c r="E2" t="n">
-        <v>4.3111</v>
+        <v>2.5457</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.8562</v>
+        <v>-0.9370000000000001</v>
       </c>
       <c r="G2" t="n">
-        <v>1.8978</v>
+        <v>-0.9535</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8547</v>
+        <v>-0.9033</v>
       </c>
       <c r="I2" t="n">
-        <v>1.0431</v>
+        <v>-0.0502</v>
       </c>
       <c r="J2" t="n">
-        <v>3.761</v>
+        <v>0.6787</v>
       </c>
       <c r="K2" t="n">
-        <v>2.9961</v>
+        <v>1.156</v>
       </c>
       <c r="L2" t="n">
-        <v>0.765</v>
+        <v>-0.4773</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.8633</v>
+        <v>-1.6322</v>
       </c>
       <c r="N2" t="n">
-        <v>-2.1414</v>
+        <v>-2.0593</v>
       </c>
       <c r="O2" t="n">
-        <v>0.2781</v>
+        <v>0.4271</v>
       </c>
       <c r="P2" t="n">
-        <v>0.2175</v>
+        <v>1.0875</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.2175</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>0.435</v>
+        <v>1.0875</v>
       </c>
       <c r="S2" t="n">
-        <v>1.6442</v>
+        <v>-0.7853</v>
       </c>
       <c r="T2" t="n">
-        <v>0.9421</v>
+        <v>-0.3929</v>
       </c>
       <c r="U2" t="n">
-        <v>0.702</v>
+        <v>-0.3924</v>
       </c>
       <c r="V2" t="n">
-        <v>-1.3045</v>
+        <v>2.2599</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.1745</v>
+        <v>2.2599</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>F. ZURBRIGGEN</t>
+          <t>E. WEMBI</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.4468</v>
+        <v>1.5378</v>
       </c>
       <c r="E3" t="n">
-        <v>2.3222</v>
+        <v>3.6406</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.8754</v>
+        <v>-2.1028</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.9535</v>
+        <v>1.8978</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.9033</v>
+        <v>0.8547</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.0502</v>
+        <v>1.0431</v>
       </c>
       <c r="J3" t="n">
-        <v>0.6787</v>
+        <v>3.761</v>
       </c>
       <c r="K3" t="n">
-        <v>1.156</v>
+        <v>2.9961</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.4773</v>
+        <v>0.765</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.6322</v>
+        <v>-1.8633</v>
       </c>
       <c r="N3" t="n">
-        <v>-2.0593</v>
+        <v>-2.1414</v>
       </c>
       <c r="O3" t="n">
-        <v>0.4271</v>
+        <v>0.2781</v>
       </c>
       <c r="P3" t="n">
-        <v>1.0875</v>
+        <v>0.2175</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-0.2175</v>
       </c>
       <c r="R3" t="n">
-        <v>1.0875</v>
+        <v>0.435</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.9472</v>
+        <v>0.727</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.6165</v>
+        <v>0.2716</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.3307</v>
+        <v>0.4554</v>
       </c>
       <c r="V3" t="n">
-        <v>2.2599</v>
+        <v>-1.3045</v>
       </c>
       <c r="W3" t="n">
-        <v>2.2599</v>
+        <v>-0.1745</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.2796</v>
+        <v>1.1053</v>
       </c>
       <c r="E4" t="n">
-        <v>4.1534</v>
+        <v>3.8866</v>
       </c>
       <c r="F4" t="n">
-        <v>-2.8738</v>
+        <v>-2.7813</v>
       </c>
       <c r="G4" t="n">
         <v>2.62</v>
@@ -766,13 +766,13 @@
         <v>1.0875</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2023</v>
+        <v>0.0279</v>
       </c>
       <c r="T4" t="n">
-        <v>0.3257</v>
+        <v>0.0589</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1234</v>
+        <v>-0.031</v>
       </c>
       <c r="V4" t="n">
         <v>-1.3252</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>V. ARTEAGA GONZALEZ</t>
+          <t>E. VICEDO AYALA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,40 +799,40 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.5206</v>
+        <v>-0.4364</v>
       </c>
       <c r="E5" t="n">
-        <v>0.056</v>
+        <v>3.7676</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.5765</v>
+        <v>-4.204</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.3924</v>
+        <v>0.0984</v>
       </c>
       <c r="H5" t="n">
-        <v>0.006</v>
+        <v>-2.3575</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3984</v>
+        <v>2.4559</v>
       </c>
       <c r="J5" t="n">
-        <v>0.9409</v>
+        <v>4.1245</v>
       </c>
       <c r="K5" t="n">
-        <v>0.7879</v>
+        <v>0.5657</v>
       </c>
       <c r="L5" t="n">
-        <v>0.153</v>
+        <v>3.5588</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.3333</v>
+        <v>-4.0261</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.7819</v>
+        <v>-2.9232</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.5514</v>
+        <v>-1.1029</v>
       </c>
       <c r="P5" t="n">
         <v>1.5225</v>
@@ -844,28 +844,28 @@
         <v>1.5225</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.0857</v>
+        <v>-0.9274</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1454</v>
+        <v>-0.3569</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.9403</v>
+        <v>-0.5705</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.5649999999999999</v>
+        <v>-1.13</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.7395</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0.1745</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>E. VICEDO AYALA</t>
+          <t>V. ARTEAGA GONZALEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,40 +877,40 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.1446</v>
+        <v>-0.5215</v>
       </c>
       <c r="E6" t="n">
-        <v>3.0286</v>
+        <v>-0.09909999999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>-4.1732</v>
+        <v>-0.4224</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0984</v>
+        <v>-0.3924</v>
       </c>
       <c r="H6" t="n">
-        <v>-2.3575</v>
+        <v>0.006</v>
       </c>
       <c r="I6" t="n">
-        <v>2.4559</v>
+        <v>-0.3984</v>
       </c>
       <c r="J6" t="n">
-        <v>4.1245</v>
+        <v>0.9409</v>
       </c>
       <c r="K6" t="n">
-        <v>0.5657</v>
+        <v>0.7879</v>
       </c>
       <c r="L6" t="n">
-        <v>3.5588</v>
+        <v>0.153</v>
       </c>
       <c r="M6" t="n">
-        <v>-4.0261</v>
+        <v>-1.3333</v>
       </c>
       <c r="N6" t="n">
-        <v>-2.9232</v>
+        <v>-0.7819</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.1029</v>
+        <v>-0.5514</v>
       </c>
       <c r="P6" t="n">
         <v>1.5225</v>
@@ -922,22 +922,22 @@
         <v>1.5225</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.6356</v>
+        <v>-1.0866</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.0959</v>
+        <v>-0.3004</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.5397</v>
+        <v>-0.7862</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.13</v>
+        <v>-0.5649999999999999</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>-0.7395</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.13</v>
+        <v>0.1745</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.8749</v>
+        <v>-2.1177</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.8711</v>
+        <v>-2.2064</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.0038</v>
+        <v>0.0887</v>
       </c>
       <c r="G7" t="n">
         <v>-1.3886</v>
@@ -1000,13 +1000,13 @@
         <v>0.2175</v>
       </c>
       <c r="S7" t="n">
-        <v>0.3837</v>
+        <v>0.1409</v>
       </c>
       <c r="T7" t="n">
-        <v>0.4711</v>
+        <v>0.1358</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.08740000000000001</v>
+        <v>0.0051</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>N. GALETTE</t>
+          <t>T. MCFADDEN</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.4842</v>
+        <v>-2.5509</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.7911</v>
+        <v>0.2077</v>
       </c>
       <c r="F8" t="n">
-        <v>0.3069</v>
+        <v>-2.7585</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.116</v>
+        <v>-3.2689</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.9885</v>
+        <v>-2.6036</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.1275</v>
+        <v>-0.6653</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.6147</v>
+        <v>-0.6199</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.1246</v>
+        <v>-0.3769</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.4901</v>
+        <v>-0.243</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.5013</v>
+        <v>-2.6491</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.8639</v>
+        <v>-2.2267</v>
       </c>
       <c r="O8" t="n">
-        <v>0.3626</v>
+        <v>-0.4224</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.6525</v>
+        <v>0.2175</v>
       </c>
       <c r="Q8" t="n">
         <v>-1.305</v>
       </c>
       <c r="R8" t="n">
-        <v>0.6525</v>
+        <v>1.5225</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2843</v>
+        <v>-0.6294</v>
       </c>
       <c r="T8" t="n">
-        <v>0.1286</v>
+        <v>-0.1274</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1557</v>
+        <v>-0.502</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>2.2599</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. SOLA IDDRISU</t>
+          <t>N. GALETTE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,58 +1111,58 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.7271</v>
+        <v>-2.831</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.2414</v>
+        <v>-3.0147</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.4857</v>
+        <v>0.1836</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.3621</v>
+        <v>-2.116</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.6816</v>
+        <v>-0.9885</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.6805</v>
+        <v>-1.1275</v>
       </c>
       <c r="J9" t="n">
-        <v>0.5706</v>
+        <v>-1.6147</v>
       </c>
       <c r="K9" t="n">
-        <v>1.2957</v>
+        <v>-0.1246</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.7251</v>
+        <v>-1.4901</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.9327</v>
+        <v>-0.5013</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.9773</v>
+        <v>-0.8639</v>
       </c>
       <c r="O9" t="n">
-        <v>0.0446</v>
+        <v>0.3626</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.5225</v>
+        <v>-0.6525</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.3926</v>
+        <v>-1.305</v>
       </c>
       <c r="R9" t="n">
-        <v>0.87</v>
+        <v>0.6525</v>
       </c>
       <c r="S9" t="n">
-        <v>0.1575</v>
+        <v>-0.0625</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4194</v>
+        <v>-0.0949</v>
       </c>
       <c r="U9" t="n">
-        <v>0.5769</v>
+        <v>0.0324</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>T. MCFADDEN</t>
+          <t>S. LITTLESON</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.0586</v>
+        <v>-2.854</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.0843</v>
+        <v>1.3925</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.9743</v>
+        <v>-4.2464</v>
       </c>
       <c r="G10" t="n">
-        <v>-3.2689</v>
+        <v>0.3425</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.6036</v>
+        <v>-0.742</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.6653</v>
+        <v>1.0846</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.6199</v>
+        <v>3.9677</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.3769</v>
+        <v>2.0138</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.243</v>
+        <v>1.9539</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.6491</v>
+        <v>-3.6252</v>
       </c>
       <c r="N10" t="n">
-        <v>-2.2267</v>
+        <v>-2.7558</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.4224</v>
+        <v>-0.8694</v>
       </c>
       <c r="P10" t="n">
-        <v>0.2175</v>
+        <v>-0.2175</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.305</v>
+        <v>-2.1751</v>
       </c>
       <c r="R10" t="n">
-        <v>1.5225</v>
+        <v>1.9576</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.1372</v>
+        <v>-1.284</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4194</v>
+        <v>-0.4002</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.7178</v>
+        <v>-0.8839</v>
       </c>
       <c r="V10" t="n">
-        <v>1.13</v>
+        <v>-1.695</v>
       </c>
       <c r="W10" t="n">
-        <v>2.2599</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.13</v>
+        <v>-1.695</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>S. LITTLESON</t>
+          <t>A. SOLA IDDRISU</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.6662</v>
+        <v>-2.8927</v>
       </c>
       <c r="E11" t="n">
-        <v>0.7652</v>
+        <v>-2.1296</v>
       </c>
       <c r="F11" t="n">
-        <v>-4.4314</v>
+        <v>-0.7631</v>
       </c>
       <c r="G11" t="n">
-        <v>0.3425</v>
+        <v>-1.3621</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.742</v>
+        <v>-0.6816</v>
       </c>
       <c r="I11" t="n">
-        <v>1.0846</v>
+        <v>-0.6805</v>
       </c>
       <c r="J11" t="n">
-        <v>3.9677</v>
+        <v>0.5706</v>
       </c>
       <c r="K11" t="n">
-        <v>2.0138</v>
+        <v>1.2957</v>
       </c>
       <c r="L11" t="n">
-        <v>1.9539</v>
+        <v>-0.7251</v>
       </c>
       <c r="M11" t="n">
-        <v>-3.6252</v>
+        <v>-1.9327</v>
       </c>
       <c r="N11" t="n">
-        <v>-2.7558</v>
+        <v>-1.9773</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.8694</v>
+        <v>0.0446</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.2175</v>
+        <v>-1.5225</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.1751</v>
+        <v>-2.3926</v>
       </c>
       <c r="R11" t="n">
-        <v>1.9576</v>
+        <v>0.87</v>
       </c>
       <c r="S11" t="n">
-        <v>-2.0962</v>
+        <v>-0.0081</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.0274</v>
+        <v>-0.3076</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.0688</v>
+        <v>0.2995</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.695</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.695</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1345,16 +1345,16 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-10.2949</v>
+        <v>-9.952400000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>7.6486</v>
+        <v>7.990899999999998</v>
       </c>
       <c r="F12" t="n">
-        <v>-17.9434</v>
+        <v>-17.9432</v>
       </c>
       <c r="G12" t="n">
-        <v>-4.522799999999999</v>
+        <v>-4.5228</v>
       </c>
       <c r="H12" t="n">
         <v>-7.802</v>
@@ -1369,7 +1369,7 @@
         <v>10.0537</v>
       </c>
       <c r="L12" t="n">
-        <v>5.068300000000001</v>
+        <v>5.0683</v>
       </c>
       <c r="M12" t="n">
         <v>-19.6448</v>
@@ -1390,16 +1390,16 @@
         <v>10.8751</v>
       </c>
       <c r="S12" t="n">
-        <v>-4.229900000000001</v>
+        <v>-3.8875</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.8565</v>
+        <v>-1.514</v>
       </c>
       <c r="U12" t="n">
-        <v>-2.3735</v>
+        <v>-2.3736</v>
       </c>
       <c r="V12" t="n">
-        <v>-2.6298</v>
+        <v>-2.629799999999999</v>
       </c>
       <c r="W12" t="n">
         <v>4.1708</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>L. NWOGBO</t>
+          <t>P. GARINO GULLOTTA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>7.2297</v>
+        <v>6.7072</v>
       </c>
       <c r="E13" t="n">
-        <v>6.8729</v>
+        <v>7.3299</v>
       </c>
       <c r="F13" t="n">
-        <v>0.3568</v>
+        <v>-0.6227</v>
       </c>
       <c r="G13" t="n">
-        <v>4.6181</v>
+        <v>1.7996</v>
       </c>
       <c r="H13" t="n">
-        <v>4.0117</v>
+        <v>2.5</v>
       </c>
       <c r="I13" t="n">
-        <v>0.6064000000000001</v>
+        <v>-0.7004</v>
       </c>
       <c r="J13" t="n">
-        <v>5.5713</v>
+        <v>4.2031</v>
       </c>
       <c r="K13" t="n">
-        <v>5.4565</v>
+        <v>4.5258</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1147</v>
+        <v>-0.3227</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.9532</v>
+        <v>-2.4036</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.4449</v>
+        <v>-2.0258</v>
       </c>
       <c r="O13" t="n">
-        <v>0.4916</v>
+        <v>-0.3778</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>1.5225</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.0875</v>
+        <v>1.5225</v>
       </c>
       <c r="S13" t="n">
-        <v>2.2419</v>
+        <v>-0.0048</v>
       </c>
       <c r="T13" t="n">
-        <v>1.8242</v>
+        <v>-0.2632</v>
       </c>
       <c r="U13" t="n">
-        <v>0.4177</v>
+        <v>0.2584</v>
       </c>
       <c r="V13" t="n">
-        <v>0.3698</v>
+        <v>3.3899</v>
       </c>
       <c r="W13" t="n">
-        <v>0.5649999999999999</v>
+        <v>3.3899</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.1952</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>P. GARINO GULLOTTA</t>
+          <t>L. NWOGBO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>6.395</v>
+        <v>5.8771</v>
       </c>
       <c r="E14" t="n">
-        <v>6.7711</v>
+        <v>5.6436</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.3761</v>
+        <v>0.2335</v>
       </c>
       <c r="G14" t="n">
-        <v>1.7996</v>
+        <v>4.6181</v>
       </c>
       <c r="H14" t="n">
-        <v>2.5</v>
+        <v>4.0117</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.7004</v>
+        <v>0.6064000000000001</v>
       </c>
       <c r="J14" t="n">
-        <v>4.2031</v>
+        <v>5.5713</v>
       </c>
       <c r="K14" t="n">
-        <v>4.5258</v>
+        <v>5.4565</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.3227</v>
+        <v>0.1147</v>
       </c>
       <c r="M14" t="n">
-        <v>-2.4036</v>
+        <v>-0.9532</v>
       </c>
       <c r="N14" t="n">
-        <v>-2.0258</v>
+        <v>-1.4449</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.3778</v>
+        <v>0.4916</v>
       </c>
       <c r="P14" t="n">
-        <v>1.5225</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R14" t="n">
-        <v>1.5225</v>
+        <v>1.0875</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.317</v>
+        <v>0.8893</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.822</v>
+        <v>0.5948</v>
       </c>
       <c r="U14" t="n">
-        <v>0.5049</v>
+        <v>0.2944</v>
       </c>
       <c r="V14" t="n">
-        <v>3.3899</v>
+        <v>0.3698</v>
       </c>
       <c r="W14" t="n">
-        <v>3.3899</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.9042</v>
+        <v>3.3628</v>
       </c>
       <c r="E15" t="n">
-        <v>3.2409</v>
+        <v>3.5761</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.3366</v>
+        <v>-0.2133</v>
       </c>
       <c r="G15" t="n">
         <v>1.2811</v>
@@ -1624,13 +1624,13 @@
         <v>0.87</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.3769</v>
+        <v>0.08169999999999999</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.274</v>
+        <v>0.0613</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1029</v>
+        <v>0.0204</v>
       </c>
       <c r="V15" t="n">
         <v>1.13</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.7364</v>
+        <v>1.9637</v>
       </c>
       <c r="E16" t="n">
-        <v>2.076</v>
+        <v>1.9643</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.3396</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="G16" t="n">
         <v>-1.0786</v>
@@ -1702,13 +1702,13 @@
         <v>1.7401</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.62</v>
+        <v>-0.3927</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.2139</v>
+        <v>-0.3256</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.4061</v>
+        <v>-0.067</v>
       </c>
       <c r="V16" t="n">
         <v>1.695</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.2151</v>
+        <v>1.3576</v>
       </c>
       <c r="E17" t="n">
-        <v>1.1654</v>
+        <v>1.2771</v>
       </c>
       <c r="F17" t="n">
-        <v>0.0497</v>
+        <v>0.0805</v>
       </c>
       <c r="G17" t="n">
         <v>0.6415</v>
@@ -1780,13 +1780,13 @@
         <v>0.87</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.8615</v>
+        <v>-0.7189</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.4795</v>
+        <v>-0.3677</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.382</v>
+        <v>-0.3512</v>
       </c>
       <c r="V17" t="n">
         <v>0.5649999999999999</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.112</v>
+        <v>0.7151</v>
       </c>
       <c r="E18" t="n">
-        <v>0.5944</v>
+        <v>0.2591</v>
       </c>
       <c r="F18" t="n">
-        <v>0.5175999999999999</v>
+        <v>0.4559</v>
       </c>
       <c r="G18" t="n">
         <v>-0.0834</v>
@@ -1858,13 +1858,13 @@
         <v>0.6525</v>
       </c>
       <c r="S18" t="n">
-        <v>1.6305</v>
+        <v>1.2335</v>
       </c>
       <c r="T18" t="n">
-        <v>0.9421</v>
+        <v>0.6069</v>
       </c>
       <c r="U18" t="n">
-        <v>0.6883</v>
+        <v>0.6267</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. VAULET</t>
+          <t>L. GIOVANNETTI</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.0571</v>
+        <v>0.2259</v>
       </c>
       <c r="E19" t="n">
-        <v>1.0445</v>
+        <v>0.5506</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.1017</v>
+        <v>-0.3246</v>
       </c>
       <c r="G19" t="n">
-        <v>0.9964</v>
+        <v>-0.5473</v>
       </c>
       <c r="H19" t="n">
-        <v>1.6547</v>
+        <v>0.0121</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.6582</v>
+        <v>-0.5594</v>
       </c>
       <c r="J19" t="n">
-        <v>3.0486</v>
+        <v>0.2225</v>
       </c>
       <c r="K19" t="n">
-        <v>3.2</v>
+        <v>0.146</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.1514</v>
+        <v>0.0765</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.0521</v>
+        <v>-0.7698</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.5453</v>
+        <v>-0.1339</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.5068</v>
+        <v>-0.6359</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.9576</v>
+        <v>0.435</v>
       </c>
       <c r="Q19" t="n">
-        <v>-3.2626</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.305</v>
+        <v>0.435</v>
       </c>
       <c r="S19" t="n">
-        <v>0.339</v>
+        <v>0.3383</v>
       </c>
       <c r="T19" t="n">
-        <v>0.1286</v>
+        <v>0.3281</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2104</v>
+        <v>0.0102</v>
       </c>
       <c r="V19" t="n">
-        <v>0.5649999999999999</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.5649999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>L. GIOVANNETTI</t>
+          <t>J. VAULET</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.6294999999999999</v>
+        <v>-0.4463</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.12</v>
+        <v>0.9328</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.5096000000000001</v>
+        <v>-1.3791</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.5473</v>
+        <v>0.9964</v>
       </c>
       <c r="H20" t="n">
-        <v>0.0121</v>
+        <v>1.6547</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.5594</v>
+        <v>-0.6582</v>
       </c>
       <c r="J20" t="n">
-        <v>0.2225</v>
+        <v>3.0486</v>
       </c>
       <c r="K20" t="n">
-        <v>0.146</v>
+        <v>3.2</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0765</v>
+        <v>-0.1514</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.7698</v>
+        <v>-2.0521</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.1339</v>
+        <v>-1.5453</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.6359</v>
+        <v>-0.5068</v>
       </c>
       <c r="P20" t="n">
-        <v>0.435</v>
+        <v>-1.9576</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-3.2626</v>
       </c>
       <c r="R20" t="n">
-        <v>0.435</v>
+        <v>1.305</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.5172</v>
+        <v>-0.0502</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.3425</v>
+        <v>0.0168</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1747</v>
+        <v>-0.067</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-0.5649999999999999</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.5349</v>
+        <v>-1.4347</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.4164</v>
+        <v>-0.1929</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.1186</v>
+        <v>-1.2418</v>
       </c>
       <c r="G21" t="n">
         <v>-2.3553</v>
@@ -2092,13 +2092,13 @@
         <v>0.2175</v>
       </c>
       <c r="S21" t="n">
-        <v>0.9933</v>
+        <v>1.0935</v>
       </c>
       <c r="T21" t="n">
-        <v>0.5396</v>
+        <v>0.7631</v>
       </c>
       <c r="U21" t="n">
-        <v>0.4538</v>
+        <v>0.3305</v>
       </c>
       <c r="V21" t="n">
         <v>-0.3904</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.7033</v>
+        <v>-2.551</v>
       </c>
       <c r="E22" t="n">
-        <v>1.8007</v>
+        <v>1.3537</v>
       </c>
       <c r="F22" t="n">
-        <v>-3.504</v>
+        <v>-3.9047</v>
       </c>
       <c r="G22" t="n">
         <v>0.0648</v>
@@ -2170,13 +2170,13 @@
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>2.3189</v>
+        <v>1.4712</v>
       </c>
       <c r="T22" t="n">
-        <v>1.2161</v>
+        <v>0.7691</v>
       </c>
       <c r="U22" t="n">
-        <v>1.1028</v>
+        <v>0.7020999999999999</v>
       </c>
       <c r="V22" t="n">
         <v>-2.9995</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.0854</v>
+        <v>-2.5845</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.8231</v>
+        <v>-1.5996</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.2623</v>
+        <v>-0.9849</v>
       </c>
       <c r="G23" t="n">
         <v>0.6207</v>
@@ -2248,13 +2248,13 @@
         <v>0.2175</v>
       </c>
       <c r="S23" t="n">
-        <v>0.4265</v>
+        <v>0.9274</v>
       </c>
       <c r="T23" t="n">
-        <v>0.4711</v>
+        <v>0.6946</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.0446</v>
+        <v>0.2328</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.2872</v>
+        <v>-2.8981</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.7634</v>
+        <v>-1.6516</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.5238</v>
+        <v>-1.2464</v>
       </c>
       <c r="G24" t="n">
         <v>-1.4347</v>
@@ -2326,13 +2326,13 @@
         <v>0.87</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.0276</v>
+        <v>-0.6384</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.6165</v>
+        <v>-0.5047</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.4111</v>
+        <v>-0.1337</v>
       </c>
       <c r="V24" t="n">
         <v>-1.695</v>
@@ -2359,10 +2359,10 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>10.295</v>
+        <v>10.2948</v>
       </c>
       <c r="E25" t="n">
-        <v>19.443</v>
+        <v>19.4431</v>
       </c>
       <c r="F25" t="n">
         <v>-9.148199999999999</v>
@@ -2404,13 +2404,13 @@
         <v>9.787599999999999</v>
       </c>
       <c r="S25" t="n">
-        <v>4.229899999999999</v>
+        <v>4.2299</v>
       </c>
       <c r="T25" t="n">
-        <v>2.3733</v>
+        <v>2.373499999999999</v>
       </c>
       <c r="U25" t="n">
-        <v>1.8565</v>
+        <v>1.8566</v>
       </c>
       <c r="V25" t="n">
         <v>2.629799999999999</v>
